--- a/data/trans_orig/IP21B-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP21B-Habitat-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2446</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2986</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4060</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,62%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2282</t>
+          <t>1681</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>5055</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3612</t>
+          <t>3919</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>655</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5531</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>27,06%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7495</t>
+          <t>7188</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5888</t>
+          <t>5834</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15315</t>
+          <t>15204</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20205</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,86%</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3549</t>
+          <t>4233</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>30,06%</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4485</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10531</t>
+          <t>9847</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>2944</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3999</t>
+          <t>3933</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>609</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5282</t>
+          <t>4760</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>32,81%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>794</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6772</t>
+          <t>6838</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>9750</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13897</t>
+          <t>13901</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>583</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5737</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1462</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8152</t>
+          <t>7536</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3318</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11486</t>
+          <t>11013</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>18,81%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19674</t>
+          <t>20129</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24730</t>
+          <t>24828</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25002</t>
+          <t>25618</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31692</t>
+          <t>31277</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47079</t>
+          <t>47552</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55247</t>
+          <t>55249</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,34%</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2821</t>
+          <t>2960</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>26,82%</t>
         </is>
       </c>
     </row>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3797</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8219</t>
+          <t>8080</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>687</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5530</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3321</t>
+          <t>3943</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7359</t>
+          <t>7323</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,75%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4971</t>
+          <t>5113</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9802</t>
+          <t>9814</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>2685</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9770</t>
+          <t>9806</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15163</t>
+          <t>15173</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,58%</t>
         </is>
       </c>
     </row>
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>574</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4421</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>568</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4486</t>
+          <t>5015</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>33,51%</t>
         </is>
       </c>
     </row>
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5355</t>
+          <t>5373</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9196</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10479</t>
+          <t>9950</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14657</t>
+          <t>14397</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>4606</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>566</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4476</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7227</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>40,42%</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4098</t>
+          <t>3615</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8544</t>
+          <t>8582</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10142</t>
+          <t>10349</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16005</t>
+          <t>16057</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,45%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>1559</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8673</t>
+          <t>8175</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>2687</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>9777</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5781</t>
+          <t>5821</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15126</t>
+          <t>15389</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19353</t>
+          <t>19851</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26357</t>
+          <t>26467</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22669</t>
+          <t>22700</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29476</t>
+          <t>29790</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45377</t>
+          <t>45114</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54722</t>
+          <t>54682</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,38%</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>36,25%</t>
         </is>
       </c>
     </row>
@@ -4775,7 +4775,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2910</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6400</t>
+          <t>6824</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>758</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6433</t>
+          <t>6807</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>45,14%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>3959</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8467</t>
+          <t>8330</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2903</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8646</t>
+          <t>8272</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13944</t>
+          <t>13870</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>91,98%</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>3732</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>62,32%</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2256</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>660</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2838</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>722</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5854</t>
+          <t>5676</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>55,89%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>756</t>
+          <t>931</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4520</t>
+          <t>4505</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2152</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4301</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9411</t>
+          <t>9433</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,89%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8339</t>
+          <t>8692</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1597</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8486</t>
+          <t>8186</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5348</t>
+          <t>5266</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14049</t>
+          <t>14230</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,94%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12889</t>
+          <t>12536</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19150</t>
+          <t>19071</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12211</t>
+          <t>12511</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18753</t>
+          <t>19100</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27876</t>
+          <t>27695</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>36577</t>
+          <t>36659</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,44%</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>1664</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2384</t>
+          <t>2835</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>55,42%</t>
         </is>
       </c>
     </row>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>329</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2732</t>
+          <t>2279</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3819</t>
+          <t>3765</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>61,96%</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7265,7 +7265,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7335,7 +7335,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,14%</t>
         </is>
       </c>
     </row>
@@ -7388,7 +7388,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3663</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>3892</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>73,4%</t>
         </is>
       </c>
     </row>
@@ -7751,7 +7751,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>901</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>908</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6519</t>
+          <t>6874</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>2390</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9845</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,71%</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4391</t>
+          <t>4433</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5942</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11696</t>
+          <t>11553</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11830</t>
+          <t>11768</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19028</t>
+          <t>19285</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>88,97%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP21B-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP21B-Habitat-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si estuvo en lista de espera en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si, en los últimos 12 meses, estuvieron en lista de espera para ingresar, al menos una noche, en un hospital en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -728,102 +728,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3014</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>13,64%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>57,21%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>576</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2444</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2472</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>14,93%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>63,31%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>64,05%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3587</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>13,64%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3588</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>14,19%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>68,09%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1295</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4073</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>14,19%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>39,31%</t>
         </is>
       </c>
     </row>
@@ -836,74 +836,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4549</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2254</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5268</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>86,36%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>42,79%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>3284</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1416</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>3860</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>85,07%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>36,69%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>35,95%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>4549</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1681</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>5268</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>86,36%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>31,91%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>11</t>
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5055</t>
+          <t>5540</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5268</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5268</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5268</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3860</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>3860</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>3860</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5268</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>5268</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>5268</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1071,67 +1071,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>1308</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3949</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13,43%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>40,55%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>1180</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3919</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3848</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>10,63%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>35,29%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1308</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3905</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>13,43%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>638</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5642</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>25,16%</t>
         </is>
       </c>
     </row>
@@ -1179,74 +1179,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8431</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5790</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9739</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>86,57%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>59,45%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>9927</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7188</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>7259</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>11107</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>89,37%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>64,71%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>65,35%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>8431</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>5834</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>9739</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>86,57%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>59,9%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>29</t>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15204</t>
+          <t>15601</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>20208</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>9739</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>9739</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>9739</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>11107</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>11107</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>11107</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>9739</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>9739</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>9739</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,107 +1409,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2863</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,85%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>38,82%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>726</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2855</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,85%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3676</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>5,16%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>38,72%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>726</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4233</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>5,16%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -1522,74 +1522,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6649</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4512</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7375</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>90,15%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>61,18%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>6706</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>6649</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>4520</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>7375</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>90,15%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>61,28%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>21</t>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9847</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1640,52 +1640,52 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>7375</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7375</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>7375</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>6706</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>6706</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>6706</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>7375</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>7375</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>7375</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3962</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,21%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>36,78%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>712</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2944</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2946</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>19,06%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>78,76%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1315</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3933</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>12,21%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>622</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4760</t>
+          <t>5420</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>37,36%</t>
         </is>
       </c>
     </row>
@@ -1865,74 +1865,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9456</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6809</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>10771</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>87,79%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>63,22%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>3026</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>794</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>3738</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>80,94%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>21,24%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>21,2%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>9456</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>6838</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>10771</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>87,79%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>63,49%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>18</t>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9750</t>
+          <t>9090</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13901</t>
+          <t>13888</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>10771</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>10771</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>10771</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>3738</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>3738</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>3738</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>10771</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>10771</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>10771</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4069</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1421</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7603</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>12,27%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>22,93%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2469</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>583</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5282</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5511</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>9,72%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>20,79%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>4069</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1877</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>7536</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>12,27%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3316</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11013</t>
+          <t>11170</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,07%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>29085</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>25551</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>31733</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>87,73%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>77,07%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>95,71%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>22942</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>20129</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>24828</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>19900</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>24773</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>90,28%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>79,21%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,71%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>29085</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>25618</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>31277</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>87,73%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47552</t>
+          <t>47395</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55249</t>
+          <t>55417</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>33154</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>33154</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>33154</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>25411</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>25411</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>25411</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>33154</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>33154</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>33154</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2485,13 +2485,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si estuvo en lista de espera en 2012 (tasa de respuesta: 97,75%)</t>
+          <t>Menores según si, en los últimos 12 meses, estuvieron en lista de espera para ingresar, al menos una noche, en un hospital en 2012 (tasa de respuesta: 97,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,107 +2670,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>682</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2962</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>9,86%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>42,77%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>682</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3120</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>9,86%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2976</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>6,18%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>45,05%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2960</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>6,18%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,96%</t>
         </is>
       </c>
     </row>
@@ -2783,74 +2783,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6243</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3963</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6925</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>90,14%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>57,23%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>4114</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>6243</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>3805</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>6925</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>90,14%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>54,95%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>14</t>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>8064</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6925</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6925</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6925</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>4114</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>4114</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>4114</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>6925</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>6925</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>6925</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>19,62%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>50,16%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2696</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5388</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5453</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>25,67%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,54%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>51,3%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1300</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3943</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>19,62%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7323</t>
+          <t>7271</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,45%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5328</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6628</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>80,38%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>49,84%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>7805</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5113</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9814</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>5048</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>9818</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>74,33%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>48,7%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>93,46%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>5328</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2685</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>6628</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>80,38%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9806</t>
+          <t>9858</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15173</t>
+          <t>15751</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>91,96%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>6628</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>6628</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>6628</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>10501</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>10501</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>10501</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>6628</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>6628</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>6628</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,92 +3356,92 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1888</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>577</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4085</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>19,31%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>41,79%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>1888</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>574</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4403</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>19,31%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>5,87%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>45,04%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1888</t>
-        </is>
-      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>581</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5015</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>29,63%</t>
         </is>
       </c>
     </row>
@@ -3469,74 +3469,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7888</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5691</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>9199</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>80,69%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>58,21%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>94,1%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>5190</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>7888</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>5373</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>9202</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>80,69%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>54,96%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>94,13%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>20</t>
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9950</t>
+          <t>10531</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14397</t>
+          <t>14384</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,12%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9776</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9776</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9776</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>5190</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>5190</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>5190</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>9776</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>9776</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>9776</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>537</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4726</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>21,69%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,87%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>51,66%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1657</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>4606</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>20,16%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>56,02%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>566</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4722</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>21,69%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>6,19%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>7071</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,71%</t>
         </is>
       </c>
     </row>
@@ -3817,69 +3817,69 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>7164</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4422</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8611</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>78,31%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>48,34%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,13%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>6564</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>3615</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>8221</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>79,84%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>43,98%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>43,97%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>7164</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>4426</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>8582</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>78,31%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>48,38%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>93,81%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>18</t>
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10349</t>
+          <t>10298</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16057</t>
+          <t>16053</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,42%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>9148</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>9148</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>9148</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>8221</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>8221</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>8221</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>9148</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>9148</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>9148</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5854</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2630</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>10136</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>18,03%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>8,1%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>31,21%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>4353</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1559</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8175</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1463</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>8427</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>15,53%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,56%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>29,17%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>5854</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2687</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>9777</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>18,03%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5821</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15389</t>
+          <t>15280</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,26%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>26623</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>22341</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>29847</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>81,97%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>68,79%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>91,9%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>23673</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>19851</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>26467</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>19599</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>26563</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>84,47%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>70,83%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>94,44%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>26623</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>22700</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>29790</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>81,97%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45114</t>
+          <t>45223</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54682</t>
+          <t>54601</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,25%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>32477</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>32477</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>32477</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>28026</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>28026</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>28026</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>32477</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>32477</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>32477</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,13 +4432,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si estuvo en lista de espera en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si, en los últimos 12 meses, estuvieron en lista de espera para ingresar, al menos una noche, en un hospital en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,107 +4617,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1494</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3933</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>22,13%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>58,25%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1494</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3861</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>22,13%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3870</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>13,96%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>57,18%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1494</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3880</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>13,96%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,15%</t>
         </is>
       </c>
     </row>
@@ -4730,74 +4730,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5258</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2819</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6752</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>77,87%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>41,75%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>3952</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>5258</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2891</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>6752</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>77,87%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>42,82%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>13</t>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6824</t>
+          <t>6834</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6752</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6752</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6752</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3952</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>3952</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>3952</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>6752</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>6752</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>6752</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3688</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13,18%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>61,56%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2575</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>758</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5129</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5021</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>28,33%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,34%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>56,44%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>790</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2993</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>13,18%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6807</t>
+          <t>6586</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>43,68%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5201</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5991</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>86,82%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>38,44%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>6513</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3959</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8330</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>4067</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>8318</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>71,67%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>43,56%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,66%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>5201</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2998</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>5991</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>86,82%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8272</t>
+          <t>8493</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13870</t>
+          <t>13772</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,33%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>5991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>5991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>5991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>9088</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>9088</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>9088</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>5991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>5991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>5991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,107 +5303,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2965</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>48,57%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>1440</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2965</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>48,57%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3663</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>24,05%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1440</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3732</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>24,05%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>61,17%</t>
         </is>
       </c>
     </row>
@@ -5416,74 +5416,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1525</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2965</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>51,43%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>3024</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1525</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2965</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>51,43%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>7</t>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2256</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2965</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2965</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2965</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>3024</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>3024</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>3024</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>2965</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>2965</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2965</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2838</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13,43%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>56,88%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2203</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>660</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4234</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4398</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>42,65%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>12,77%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>81,98%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>670</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2881</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>13,43%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>710</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5676</t>
+          <t>5720</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>56,33%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4320</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2152</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4990</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>86,57%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>43,12%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>2962</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>931</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4505</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>57,35%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>18,02%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>87,23%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>4320</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2109</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4990</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>86,57%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4479</t>
+          <t>4435</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9433</t>
+          <t>9445</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>93,01%</t>
         </is>
       </c>
     </row>
@@ -5877,52 +5877,52 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>4990</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>4990</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>4990</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
           <t>5165</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>5165</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>5165</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>4990</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>4990</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>4990</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4394</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1642</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8458</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>21,23%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7,93%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>40,87%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>4777</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2157</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8692</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2089</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>8479</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>22,51%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>10,16%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>40,95%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>4394</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1597</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>8186</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>21,23%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5266</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14230</t>
+          <t>14107</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,65%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>12239</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>19055</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>78,77%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>59,13%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>92,07%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>16451</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>12536</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>19071</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>12749</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>19139</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>77,49%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>59,05%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>89,84%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>16303</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>12511</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>19100</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>78,77%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27695</t>
+          <t>27818</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>36659</t>
+          <t>36809</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,8%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>20697</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>20697</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>20697</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>21228</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>21228</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>21228</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>20697</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>20697</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>20697</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6379,13 +6379,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si estuvo en lista de espera en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si, en los últimos 12 meses, estuvieron en lista de espera para ingresar, al menos una noche, en un hospital en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,107 +6564,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1664</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>29,59%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>32,66%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>83,47%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>87,94%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2396</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>13,62%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2835</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>11,53%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>52,04%</t>
         </is>
       </c>
     </row>
@@ -6677,74 +6677,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2684</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1403</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>329</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1993</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>70,41%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>16,53%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1292</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1919</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>67,34%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>12,06%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>3122</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>8</t>
@@ -6752,27 +6752,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>4525</t>
+          <t>3976</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2279</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5115</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2684</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2684</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2684</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1993</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1993</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1993</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>5115</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5115</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5115</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,107 +6907,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3704</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>30,12%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>81,84%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1430</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3765</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>29,94%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3796</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>21,56%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>78,85%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1430</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4165</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>21,27%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>60,04%</t>
         </is>
       </c>
     </row>
@@ -7020,74 +7020,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3163</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>856</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4526</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>69,88%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>18,92%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1947</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1797</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>3345</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1010</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>4775</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>70,06%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>21,15%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>7</t>
@@ -7095,27 +7095,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2550</t>
+          <t>2527</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>6323</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>4526</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>4526</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>4526</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1947</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1947</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1947</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4775</t>
+          <t>1797</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4775</t>
+          <t>1797</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4775</t>
+          <t>1797</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>6323</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>6323</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>6323</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,97 +7250,97 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1653</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1730</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3544</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>36,45%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3742</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>39,16%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>78,14%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>84,71%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1730</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1653</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>84,71%</t>
         </is>
       </c>
     </row>
@@ -7363,74 +7363,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2883</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>991</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4536</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>63,55%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>21,84%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2688</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4418</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>60,84%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>15,3%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>5</t>
@@ -7438,27 +7438,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>676</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4536</t>
+          <t>4418</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7476,72 +7476,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>4536</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4536</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4536</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4418</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4418</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4418</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>4536</t>
+          <t>4418</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4536</t>
+          <t>4418</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4536</t>
+          <t>4418</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,107 +7593,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1636</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3310</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>39,76%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>80,43%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1771</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1636</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3662</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>38,81%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3541</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>33,96%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>80,26%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1771</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3892</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>33,4%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>73,52%</t>
         </is>
       </c>
     </row>
@@ -7706,74 +7706,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2479</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>811</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4115</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>60,24%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>19,71%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>739</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2792</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>901</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4563</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>61,19%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>19,74%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>6</t>
@@ -7781,27 +7781,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>4115</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>4115</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>4115</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>739</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>739</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>739</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>702</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>702</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>702</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2999</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>877</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6332</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>26,48%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7,75%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>55,91%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2243</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4782</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>24,34%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6,65%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>51,89%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9907</t>
+          <t>9061</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>44,95%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>8326</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4993</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>10448</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>73,52%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>44,09%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>92,25%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>6972</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>4433</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8602</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>75,66%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>48,11%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>93,35%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9260</t>
+          <t>6478</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11553</t>
+          <t>8169</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>16232</t>
+          <t>14804</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11768</t>
+          <t>11099</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19285</t>
+          <t>17816</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,37%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>11325</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>11325</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>11325</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>9215</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>9215</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>9215</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>21675</t>
+          <t>20160</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>21675</t>
+          <t>20160</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>21675</t>
+          <t>20160</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
